--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -908,10 +908,10 @@
     <t>身體質量指數(BMI)</t>
   </si>
   <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>Body Mass Index (BMI).</t>
+  </si>
+  <si>
+    <t>additional codes that translate or map to this code are allowed.  For example a more granular LOINC code or code that is used locally in a system.</t>
   </si>
   <si>
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
@@ -923,17 +923,25 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -1040,7 +1048,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1051,9 +1059,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1406,7 +1411,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1438,7 +1443,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1561,7 +1566,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1641,7 +1646,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1691,7 +1696,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1727,7 +1732,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1850,12 +1855,6 @@
   <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -2258,7 +2257,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5557,7 +5556,7 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>285</v>
@@ -5630,36 +5629,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5774,10 +5773,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5894,10 +5893,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5969,7 +5968,7 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -6014,13 +6013,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
@@ -6138,10 +6137,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6256,10 +6255,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6376,10 +6375,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6421,7 +6420,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>20</v>
@@ -6498,10 +6497,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6618,10 +6617,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6661,7 +6660,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>20</v>
@@ -6738,10 +6737,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6858,10 +6857,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6980,10 +6979,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7102,10 +7101,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7128,19 +7127,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7189,7 +7188,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7204,19 +7203,19 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>20</v>
@@ -7224,10 +7223,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7250,16 +7249,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7309,7 +7308,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7330,13 +7329,13 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>20</v>
@@ -7344,14 +7343,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7370,19 +7369,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7431,7 +7430,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7446,19 +7445,19 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>20</v>
@@ -7466,14 +7465,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7492,19 +7491,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7553,7 +7552,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7562,25 +7561,25 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>20</v>
@@ -7588,10 +7587,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7614,16 +7613,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7673,7 +7672,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7694,13 +7693,13 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>20</v>
@@ -7708,10 +7707,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7734,17 +7733,17 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7793,7 +7792,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7808,19 +7807,19 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -7828,10 +7827,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7854,19 +7853,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7903,17 +7902,17 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7922,7 +7921,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7931,30 +7930,30 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7976,19 +7975,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8037,7 +8036,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8046,7 +8045,7 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -8055,27 +8054,27 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8190,10 +8189,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8310,10 +8309,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8336,19 +8335,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8397,7 +8396,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8418,10 +8417,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8432,10 +8431,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8461,20 +8460,20 @@
         <v>112</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>20</v>
@@ -8498,10 +8497,10 @@
         <v>181</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8519,7 +8518,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8539,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8554,10 +8553,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8583,14 +8582,14 @@
         <v>204</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8639,7 +8638,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8660,10 +8659,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8674,10 +8673,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8703,21 +8702,21 @@
         <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>20</v>
@@ -8759,7 +8758,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8768,7 +8767,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8780,10 +8779,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8794,10 +8793,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8823,23 +8822,23 @@
         <v>112</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>20</v>
@@ -8881,7 +8880,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8902,10 +8901,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8916,10 +8915,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8945,16 +8944,16 @@
         <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8982,10 +8981,10 @@
         <v>290</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -9003,7 +9002,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9012,7 +9011,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9027,7 +9026,7 @@
         <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9038,14 +9037,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9067,16 +9066,16 @@
         <v>189</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9104,10 +9103,10 @@
         <v>290</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -9125,7 +9124,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9143,27 +9142,27 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9186,19 +9185,19 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9247,7 +9246,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9268,10 +9267,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9282,10 +9281,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9311,13 +9310,13 @@
         <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9347,7 +9346,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9365,7 +9364,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9383,27 +9382,27 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9429,16 +9428,16 @@
         <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9467,7 +9466,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9485,7 +9484,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9506,10 +9505,10 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9520,10 +9519,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,16 +9545,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9605,7 +9604,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9623,27 +9622,27 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9666,16 +9665,16 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9725,7 +9724,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9743,27 +9742,27 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9786,19 +9785,19 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9847,7 +9846,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9859,7 +9858,7 @@
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9868,10 +9867,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9882,10 +9881,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10000,10 +9999,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10120,14 +10119,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10149,10 +10148,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10207,7 +10206,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10242,10 +10241,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10268,13 +10267,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10325,7 +10324,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10334,7 +10333,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10346,10 +10345,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10360,10 +10359,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10386,13 +10385,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10443,7 +10442,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10452,7 +10451,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10464,10 +10463,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10478,10 +10477,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10507,16 +10506,16 @@
         <v>189</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10544,10 +10543,10 @@
         <v>116</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10565,7 +10564,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10583,13 +10582,13 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10600,10 +10599,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10629,16 +10628,16 @@
         <v>189</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10663,13 +10662,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10687,7 +10686,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10705,13 +10704,13 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10722,10 +10721,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10748,17 +10747,17 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10807,7 +10806,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10831,7 +10830,7 @@
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10842,10 +10841,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10871,10 +10870,10 @@
         <v>204</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10925,7 +10924,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10946,10 +10945,10 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10960,10 +10959,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10986,16 +10985,16 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11045,7 +11044,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11066,10 +11065,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11080,10 +11079,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11106,16 +11105,16 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11165,7 +11164,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11186,10 +11185,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11200,10 +11199,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11226,19 +11225,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11287,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11299,7 +11298,7 @@
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -11308,10 +11307,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11322,10 +11321,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11440,10 +11439,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11560,14 +11559,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11589,10 +11588,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -11647,7 +11646,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11682,10 +11681,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11711,16 +11710,16 @@
         <v>189</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11769,7 +11768,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>92</v>
@@ -11787,16 +11786,16 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>588</v>
+        <v>296</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>589</v>
+        <v>297</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>20</v>
@@ -11842,7 +11841,7 @@
         <v>594</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11912,16 +11911,16 @@
         <v>598</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="81">
@@ -11964,7 +11963,7 @@
         <v>602</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11992,10 +11991,10 @@
         <v>290</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -12037,7 +12036,7 @@
         <v>135</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12055,7 +12054,7 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12077,16 +12076,16 @@
         <v>189</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12114,10 +12113,10 @@
         <v>290</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -12153,19 +12152,19 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12205,10 +12204,10 @@
         <v>607</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12278,10 +12277,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
+++ b/docs/StructureDefinition-PASportObservationBodyMassIndex.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
